--- a/data/products-master.xlsx
+++ b/data/products-master.xlsx
@@ -10,7 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="products-master" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily-check" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="exceptions" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sources" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ignored-by-product-control" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sources" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,7 +441,7 @@
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="48" customWidth="1" min="8" max="8"/>
     <col width="48" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -595,7 +596,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>缺平台</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3268,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -3311,7 +3312,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -3355,7 +3356,7 @@
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -3399,7 +3400,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3444,7 @@
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -3487,7 +3488,7 @@
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3532,7 @@
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -3575,7 +3576,7 @@
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -3619,7 +3620,7 @@
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3664,7 @@
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3708,7 @@
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3752,7 @@
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -3795,7 +3796,7 @@
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -3839,7 +3840,7 @@
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -3883,7 +3884,7 @@
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3928,7 @@
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -3971,7 +3972,7 @@
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4016,7 @@
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4060,7 @@
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4104,7 @@
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4148,7 @@
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4192,7 @@
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4236,7 @@
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4280,7 @@
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -4323,7 +4324,7 @@
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -4367,7 +4368,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -4411,7 +4412,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4456,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4500,7 @@
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4544,7 @@
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4588,7 @@
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -4631,7 +4632,7 @@
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -6251,7 +6252,7 @@
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -6295,7 +6296,7 @@
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -6339,7 +6340,7 @@
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6384,7 @@
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6428,7 @@
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -6471,7 +6472,7 @@
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -6515,7 +6516,7 @@
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6560,7 @@
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6604,7 @@
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -6647,7 +6648,7 @@
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -6691,7 +6692,7 @@
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -6735,7 +6736,7 @@
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -6779,7 +6780,7 @@
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -6823,7 +6824,7 @@
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -6867,7 +6868,7 @@
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6912,7 @@
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -6955,7 +6956,7 @@
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -6999,7 +7000,7 @@
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -7043,7 +7044,7 @@
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
-          <t>缺平台 / 图片缺失 / 视频缺失</t>
+          <t>ignored_by_product_control=true / historical=true</t>
         </is>
       </c>
     </row>
@@ -8158,11 +8159,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8184,43 +8185,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>161</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>缺产品数量</t>
+          <t>主库总数</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>75</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>重复产品数量</t>
+          <t>忽略历史产品数</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>价格异常数量</t>
+          <t>缺产品数量</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>分类异常数量</t>
+          <t>重复产品数量</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -8230,44 +8231,64 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>图片缺失数量</t>
+          <t>价格异常数量</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>51</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>视频缺失数量</t>
+          <t>分类异常数量</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>图片完整率</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>68.3%</t>
-        </is>
+          <t>图片缺失数量</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>视频缺失数量</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>图片完整率</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>视频完整率</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>37.9%</t>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>55.5%</t>
         </is>
       </c>
     </row>
@@ -8282,14 +8303,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E234"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="44" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8369,7 +8390,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>firestore, website</t>
+          <t>firestore</t>
         </is>
       </c>
     </row>
@@ -8381,22 +8402,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>funda-premium-17-pro-max</t>
+          <t>iphone-oled-12-12pro</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Funda Premium Aluminio</t>
+          <t>Pantalla para iPhone 12 / 12 Pro</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Estilo iPhone 17 Pro Max</t>
+          <t>iPhone 12 / 12 Pro OLED PREMIUM</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>website</t>
+          <t>firestore</t>
         </is>
       </c>
     </row>
@@ -8408,22 +8429,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>iphone-oled-12-12pro</t>
+          <t>iphone-oled-12mini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 12 / 12 Pro</t>
+          <t>Pantalla para iPhone 12 mini</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>iPhone 12 / 12 Pro OLED PREMIUM</t>
+          <t>iPhone 12 mini OLED PREMIUM</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>firestore</t>
+          <t>firestore, app</t>
         </is>
       </c>
     </row>
@@ -8435,17 +8456,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>iphone-oled-12mini</t>
+          <t>iphone-oled-13mini</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 12 mini</t>
+          <t>Pantalla para iPhone 13 mini</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>iPhone 12 mini OLED PREMIUM</t>
+          <t>iPhone 13 mini OLED PREMIUM</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -8462,17 +8483,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>iphone-oled-13mini</t>
+          <t>iphone-oled-15plus</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 13 mini</t>
+          <t>Pantalla para iPhone 15 Plus</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>iPhone 13 mini OLED PREMIUM</t>
+          <t>iPhone 15 Plus OLED PREMIUM</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -8489,17 +8510,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>iphone-oled-15plus</t>
+          <t>iphone-oled-16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 15 Plus</t>
+          <t>Pantalla para iPhone 16</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>iPhone 15 Plus OLED PREMIUM</t>
+          <t>iPhone 16 OLED PREMIUM</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -8516,17 +8537,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>iphone-oled-16</t>
+          <t>iphone-oled-16plus</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 16</t>
+          <t>Pantalla para iPhone 16 Plus</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>iPhone 16 OLED PREMIUM</t>
+          <t>iPhone 16 Plus OLED PREMIUM</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -8543,22 +8564,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>iphone-oled-16plus</t>
+          <t>micas-hd-clear-50</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 16 Plus</t>
+          <t>Micas HD Clear</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>iPhone 16 Plus OLED PREMIUM</t>
+          <t>Paquete 50 piezas</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>firestore, app</t>
+          <t>website</t>
         </is>
       </c>
     </row>
@@ -8570,17 +8591,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>micas-hd-clear-50</t>
+          <t>micas-mate-corte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Micas HD Clear</t>
+          <t>Micas Mate</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Paquete 50 piezas</t>
+          <t>Peliculas para corte</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -8597,17 +8618,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>micas-mate-corte</t>
+          <t>micas-privacidad-corte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Micas Mate</t>
+          <t>Micas Privacidad</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Peliculas para corte</t>
+          <t>Peliculas privacy</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -8624,17 +8645,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>micas-privacidad-corte</t>
+          <t>s1-ai-classic</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Micas Privacidad</t>
+          <t>HAODE AI CLASSIC S1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Peliculas privacy</t>
+          <t>Gafas AI classic</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -8651,22 +8672,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>s1-ai-classic</t>
+          <t>samsung-oled-note-9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>HAODE AI CLASSIC S1</t>
+          <t>Pantalla para Samsung Note 9</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Gafas AI classic</t>
+          <t>Samsung Note 9 OLED CON MARCO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>website</t>
+          <t>firestore, app</t>
         </is>
       </c>
     </row>
@@ -8678,17 +8699,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>samsung-oled-note-9</t>
+          <t>samsung-oled-s20</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pantalla para Samsung Note 9</t>
+          <t>Pantalla para Samsung S20</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Samsung Note 9 OLED CON MARCO</t>
+          <t>Samsung S20 OLED CON MARCO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -8705,17 +8726,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>samsung-oled-s20</t>
+          <t>samsung-oled-s20-ultra</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pantalla para Samsung S20</t>
+          <t>Pantalla para Samsung S20 Ultra</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Samsung S20 OLED CON MARCO</t>
+          <t>Samsung S20 Ultra OLED CON MARCO</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -8732,17 +8753,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>samsung-oled-s20-ultra</t>
+          <t>samsung-oled-s21</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pantalla para Samsung S20 Ultra</t>
+          <t>Pantalla para Samsung S21</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Samsung S20 Ultra OLED CON MARCO</t>
+          <t>Samsung S21 OLED CON MARCO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8759,17 +8780,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>samsung-oled-s21</t>
+          <t>samsung-oled-s21-plus</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pantalla para Samsung S21</t>
+          <t>Pantalla para Samsung S21 Plus</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Samsung S21 OLED CON MARCO</t>
+          <t>Samsung S21 Plus OLED CON MARCO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8786,17 +8807,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>samsung-oled-s21-plus</t>
+          <t>samsung-oled-s22-plus</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pantalla para Samsung S21 Plus</t>
+          <t>Pantalla para Samsung S22 Plus</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Samsung S21 Plus OLED CON MARCO</t>
+          <t>Samsung S22 Plus OLED CON MARCO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8813,17 +8834,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>samsung-oled-s22-plus</t>
+          <t>samsung-oled-s23-plus</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pantalla para Samsung S22 Plus</t>
+          <t>Pantalla para Samsung S23 Plus</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Samsung S22 Plus OLED CON MARCO</t>
+          <t>Samsung S23 Plus OLED CON MARCO</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8840,17 +8861,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>samsung-oled-s23-plus</t>
+          <t>samsung-oled-s24-plus</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pantalla para Samsung S23 Plus</t>
+          <t>Pantalla para Samsung S24 Plus</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Samsung S23 Plus OLED CON MARCO</t>
+          <t>Samsung S24 Plus OLED CON MARCO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -8867,17 +8888,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>samsung-oled-s24-plus</t>
+          <t>samsung-oled-s9-plus</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pantalla para Samsung S24 Plus</t>
+          <t>Pantalla para Samsung S9 Plus</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Samsung S24 Plus OLED CON MARCO</t>
+          <t>Samsung S9 Plus OLED CON MARCO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -8894,22 +8915,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>samsung-oled-s9-plus</t>
+          <t>w630-ai-pro</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pantalla para Samsung S9 Plus</t>
+          <t>W630 AI PRO</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Samsung S9 Plus OLED CON MARCO</t>
+          <t>Gafas AI blancas</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>firestore, app</t>
+          <t>website</t>
         </is>
       </c>
     </row>
@@ -8921,17 +8942,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>w630-ai-pro</t>
+          <t>x200t-cortadora-micas</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>W630 AI PRO</t>
+          <t>HAODE X200T Cortadora Inteligente de Micas</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Gafas AI blancas</t>
+          <t>X200T</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -8943,1426 +8964,1218 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>价格错误</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>x200t-cortadora-micas</t>
+          <t>iphone-incell-12promax</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HAODE X200T Cortadora Inteligente de Micas</t>
+          <t>Pantalla para iPhone 12 Pro Max</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>X200T</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>website</t>
-        </is>
-      </c>
+          <t>iPhone 12 Pro Max INCELL FHD</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>价格错误</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>pantallas-iphone-incell-iphone-x-pantalla-para-iphone-x</t>
+          <t>iphone-incell-14</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone X</t>
+          <t>Pantalla para iPhone 14</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>iPhone 14 INCELL FHD</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>价格错误</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>pantallas-iphone-incell-iphone-xs-pantalla-para-iphone-xs</t>
+          <t>iphone-incell-14plus</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone XS</t>
+          <t>Pantalla para iPhone 14 Plus</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>XS</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>iPhone 14 Plus INCELL FHD</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>价格错误</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>pantallas-iphone-oled-iphone-xs-pantalla-para-iphone-xs</t>
+          <t>iphone-incell-15plus</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone XS</t>
+          <t>Pantalla para iPhone 15 Plus</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>XS</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>iPhone 15 Plus INCELL FHD</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>价格错误</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>pantallas-iphone-incell-iphone-xr-pantalla-para-iphone-xr</t>
+          <t>iphone-oled-13promax</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone XR</t>
+          <t>Pantalla para iPhone 13 Pro Max</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>XR</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>iPhone 13 Pro Max OLED PREMIUM</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>价格错误</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>pantallas-iphone-incell-iphone-11-pantalla-para-iphone-11</t>
+          <t>samsung-incell-s20-plus</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 11</t>
+          <t>Pantalla para Samsung S20 Plus</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Samsung S20 Plus INCELL CON MARCO</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>价格错误</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>pantallas-iphone-oled-iphone-11-pantalla-para-iphone-11</t>
+          <t>samsung-incell-s9-plus</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 11</t>
+          <t>Pantalla para Samsung S9 Plus</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Samsung S9 Plus INCELL CON MARCO</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>pantallas-iphone-incell-iphone-11pro-pantalla-para-iphone-11pro</t>
+          <t>aimb-g5-ai-sports</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 11PRO</t>
+          <t>AIMB-G5 AI SPORTS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>11PRO</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Gafas AI deportivas</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>pantallas-iphone-incell-iphone-xs-max-pantalla-para-iphone-xs-max</t>
+          <t>iphone-incell-16e</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone XS MAX</t>
+          <t>Pantalla para iPhone 16e</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>XS MAX</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>iPhone 16e INCELL FHD</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>pantallas-iphone-oled-iphone-xs-max-pantalla-para-iphone-xs-max</t>
+          <t>iphone-incell-16plus</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone XS MAX</t>
+          <t>Pantalla para iPhone 16 Plus</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>XS MAX</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>iPhone 16 Plus INCELL FHD</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>pantallas-iphone-incell-iphone-11pro-max-pantalla-para-iphone-11pro-max</t>
+          <t>iphone-incell-16pro</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 11PRO MAX</t>
+          <t>Pantalla para iPhone 16 Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>11PRO MAX</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>iPhone 16 Pro INCELL FHD</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>pantallas-iphone-oled-iphone-11pro-max-pantalla-para-iphone-11pro-max</t>
+          <t>iphone-incell-16promax</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 11PRO MAX</t>
+          <t>Pantalla para iPhone 16 Pro Max</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>11PRO MAX</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>iPhone 16 Pro Max INCELL FHD</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>pantallas-iphone-incell-iphone-12mini-pantalla-para-iphone-12mini</t>
+          <t>iphone-incell-17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 12mini</t>
+          <t>Pantalla para iPhone 17</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>12mini</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>iPhone 17 INCELL FHD</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>pantallas-iphone-incell-iphone-12-12pro-pantalla-para-iphone-12-12pro</t>
+          <t>iphone-incell-17air</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 12/12PRO</t>
+          <t>Pantalla para iPhone 17 Air</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>12/12PRO</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>iPhone 17 Air INCELL FHD</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>pantallas-iphone-oled-iphone-12-12pro-pantalla-para-iphone-12-12pro</t>
+          <t>iphone-incell-17pro</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 12/12PRO</t>
+          <t>Pantalla para iPhone 17 Pro</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>12/12PRO</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>iPhone 17 Pro INCELL FHD</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>pantallas-iphone-incell-iphone-12pro-max-pantalla-para-iphone-12pro-max</t>
+          <t>iphone-incell-17promax</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 12PRO MAX</t>
+          <t>Pantalla para iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>12PRO MAX</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>iPhone 17 Pro Max INCELL FHD</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>pantallas-iphone-oled-iphone-12pro-max-pantalla-para-iphone-12pro-max</t>
+          <t>iphone-oled-16promax</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 12PRO MAX</t>
+          <t>Pantalla para iPhone 16 Pro Max Soft OLED</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>12PRO MAX</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>iPhone 16 Pro Max SOFT OLED PREMIUM MOVE IC</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>pantallas-iphone-incell-iphone-13-mini-pantalla-para-iphone-13-mini</t>
+          <t>micas-hd-clear-50</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 13 mini</t>
+          <t>Micas HD Clear</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>13 mini</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Paquete 50 piezas</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>pantallas-iphone-incell-iphone-13-pantalla-para-iphone-13</t>
+          <t>micas-mate-corte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 13</t>
+          <t>Micas Mate</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Peliculas para corte</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>pantallas-iphone-oled-iphone-13-pantalla-para-iphone-13</t>
+          <t>micas-privacidad-corte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 13</t>
+          <t>Micas Privacidad</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Peliculas privacy</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>pantallas-iphone-incell-iphone-13pro-pantalla-para-iphone-13pro</t>
+          <t>s1-ai-classic</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 13PRO</t>
+          <t>HAODE AI CLASSIC S1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>13PRO</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Gafas AI classic</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>pantallas-iphone-oled-iphone-13pro-pantalla-para-iphone-13pro</t>
+          <t>samsung-incell-note-10-plus</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 13PRO</t>
+          <t>Pantalla para Samsung Note 10 Plus</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>13PRO</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Samsung Note 10 Plus INCELL CON MARCO</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>pantallas-iphone-incell-iphone-13pro-max-pantalla-para-iphone-13pro-max</t>
+          <t>samsung-incell-note-20-ultra</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 13PRO MAX</t>
+          <t>Pantalla para Samsung Note 20 Ultra</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>13PRO MAX</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Samsung Note 20 Ultra INCELL CON MARCO</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>pantallas-iphone-oled-iphone-13pro-max-pantalla-para-iphone-13pro-max</t>
+          <t>samsung-incell-note-8</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 13PRO MAX</t>
+          <t>Pantalla para Samsung Note 8</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>13PRO MAX</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Samsung Note 8 INCELL CON MARCO</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>pantallas-iphone-incell-iphone-14-pantalla-para-iphone-14</t>
+          <t>samsung-incell-note-9</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 14</t>
+          <t>Pantalla para Samsung Note 9</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Samsung Note 9 INCELL CON MARCO</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>pantallas-iphone-oled-iphone-14-pantalla-para-iphone-14</t>
+          <t>samsung-incell-s20-ultra</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 14</t>
+          <t>Pantalla para Samsung S20 Ultra</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Samsung S20 Ultra INCELL CON MARCO</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>pantallas-iphone-incell-iphone-14-plus-pantalla-para-iphone-14-plus</t>
+          <t>samsung-incell-s21</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 14 plus</t>
+          <t>Pantalla para Samsung S21</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>14 plus</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Samsung S21 INCELL CON MARCO</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>pantallas-iphone-oled-iphone-14-plus-pantalla-para-iphone-14-plus</t>
+          <t>samsung-incell-s21-ultra</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 14 plus</t>
+          <t>Pantalla para Samsung S21 Ultra</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>14 plus</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Samsung S21 Ultra INCELL CON MARCO</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>pantallas-iphone-incell-iphone-14pro-pantalla-para-iphone-14pro</t>
+          <t>samsung-incell-s24-ultra</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 14PRO</t>
+          <t>Pantalla para Samsung S24 Ultra</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>14PRO</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Samsung S24 Ultra INCELL CON MARCO</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>pantallas-iphone-oled-iphone-14pro-pantalla-para-iphone-14pro</t>
+          <t>samsung-incell-s8</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 14PRO</t>
+          <t>Pantalla para Samsung S8</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>14PRO</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Samsung S8 INCELL CON MARCO</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>pantallas-iphone-incell-iphone-14pro-max-pantalla-para-iphone-14pro-max</t>
+          <t>samsung-incell-s9</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 14PRO MAX</t>
+          <t>Pantalla para Samsung S9</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>14PRO MAX</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Samsung S9 INCELL CON MARCO</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>pantallas-iphone-oled-iphone-14pro-max-pantalla-para-iphone-14pro-max</t>
+          <t>samsung-incell-s9-plus</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 14PRO MAX</t>
+          <t>Pantalla para Samsung S9 Plus</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>14PRO MAX</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Samsung S9 Plus INCELL CON MARCO</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>pantallas-iphone-incell-iphone-15-pantalla-para-iphone-15</t>
+          <t>samsung-oled-note-10</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 15</t>
+          <t>Pantalla para Samsung Note 10</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Samsung Note 10 OLED CON MARCO</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>pantallas-iphone-oled-iphone-15-pantalla-para-iphone-15</t>
+          <t>samsung-oled-note-10-plus</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 15</t>
+          <t>Pantalla para Samsung Note 10 Plus</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Samsung Note 10 Plus OLED CON MARCO</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>pantallas-iphone-incell-iphone-15-plus-pantalla-para-iphone-15-plus</t>
+          <t>samsung-oled-note-20</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 15 plus</t>
+          <t>Pantalla para Samsung Note 20</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>15 plus</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Samsung Note 20 OLED CON MARCO</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>pantallas-iphone-incell-iphone-15pro-pantalla-para-iphone-15pro</t>
+          <t>samsung-oled-note-20-ultra</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 15PRO</t>
+          <t>Pantalla para Samsung Note 20 Ultra</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>15PRO</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Samsung Note 20 Ultra OLED CON MARCO</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>pantallas-iphone-oled-iphone-15pro-pantalla-para-iphone-15pro</t>
+          <t>samsung-oled-note-9</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 15PRO</t>
+          <t>Pantalla para Samsung Note 9</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>15PRO</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Samsung Note 9 OLED CON MARCO</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>pantallas-iphone-incell-iphone-15pro-max-pantalla-para-iphone-15pro-max</t>
+          <t>samsung-oled-s20</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 15PRO MAX</t>
+          <t>Pantalla para Samsung S20</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>15PRO MAX</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Samsung S20 OLED CON MARCO</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>pantallas-iphone-oled-iphone-15pro-max-pantalla-para-iphone-15pro-max</t>
+          <t>samsung-oled-s20-ultra</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 15PRO MAX</t>
+          <t>Pantalla para Samsung S20 Ultra</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>15PRO MAX</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Samsung S20 Ultra OLED CON MARCO</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>pantallas-iphone-incell-iphone-16-pantalla-para-iphone-16</t>
+          <t>samsung-oled-s21</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 16</t>
+          <t>Pantalla para Samsung S21</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Samsung S21 OLED CON MARCO</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>pantallas-iphone-incell-iphone-16e-pantalla-para-iphone-16e</t>
+          <t>samsung-oled-s21-plus</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 16E</t>
+          <t>Pantalla para Samsung S21 Plus</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>16E</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Samsung S21 Plus OLED CON MARCO</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>pantallas-iphone-oled-iphone-16e-pantalla-para-iphone-16e</t>
+          <t>samsung-oled-s22-plus</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 16E</t>
+          <t>Pantalla para Samsung S22 Plus</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>16E</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Samsung S22 Plus OLED CON MARCO</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>pantallas-iphone-incell-iphone-16plus-pantalla-para-iphone-16plus</t>
+          <t>samsung-oled-s23-plus</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 16PLUS</t>
+          <t>Pantalla para Samsung S23 Plus</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>16PLUS</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Samsung S23 Plus OLED CON MARCO</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>pantallas-iphone-incell-iphone-16pro-pantalla-para-iphone-16pro</t>
+          <t>samsung-oled-s24-plus</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 16PRO</t>
+          <t>Pantalla para Samsung S24 Plus</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>16PRO</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Samsung S24 Plus OLED CON MARCO</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>pantallas-iphone-oled-iphone-16pro-pantalla-para-iphone-16pro</t>
+          <t>samsung-oled-s9-plus</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 16PRO</t>
+          <t>Pantalla para Samsung S9 Plus</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>16PRO</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Samsung S9 Plus OLED CON MARCO</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>pantallas-iphone-oled-iphone-16-promax-pantalla-para-iphone-16-promax</t>
+          <t>w630-ai-pro</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 16 PROMAX</t>
+          <t>W630 AI PRO</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>16 PROMAX</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Gafas AI blancas</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>pantallas-iphone-incell-iphone-16-promax-pantalla-para-iphone-16-promax</t>
+          <t>x200t-cortadora-micas</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 16 PROMAX</t>
+          <t>HAODE X200T Cortadora Inteligente de Micas</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>16 PROMAX</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>X200T</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>pantallas-iphone-incell-iphone-17-pantalla-para-iphone-17</t>
+          <t>samsung-incell-s10e</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 17</t>
+          <t>Pantalla para Samsung S10E</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Samsung S10E INCELL CON MARCO</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>pantallas-iphone-incell-iphone-17pro-pantalla-para-iphone-17pro</t>
+          <t>samsung-incell-s21-fe</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 17PRO</t>
+          <t>Pantalla para Samsung S21 FE</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>17PRO</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Samsung S21 FE INCELL CON MARCO</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>pantallas-iphone-incell-iphone-17-air-pantalla-para-iphone-17-air</t>
+          <t>samsung-incell-s21-plus</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 17 AIR</t>
+          <t>Pantalla para Samsung S21 Plus</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>17 AIR</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Samsung S21 Plus INCELL CON MARCO</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>pantallas-iphone-incell-iphone-17e-pantalla-para-iphone-17e</t>
+          <t>samsung-incell-s22</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 17E</t>
+          <t>Pantalla para Samsung S22</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>17E</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Samsung S22 INCELL CON MARCO</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>缺产品</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>pantallas-iphone-incell-iphone-17-promax-pantalla-para-iphone-17-promax</t>
+          <t>samsung-incell-s22-plus</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 17 PROMAX</t>
+          <t>Pantalla para Samsung S22 Plus</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>17 PROMAX</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>firestore, website, app</t>
-        </is>
-      </c>
+          <t>Samsung S22 Plus INCELL CON MARCO</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>价格错误</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>iphone-incell-12promax</t>
+          <t>samsung-incell-s23</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 12 Pro Max</t>
+          <t>Pantalla para Samsung S23</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>iPhone 12 Pro Max INCELL FHD</t>
+          <t>Samsung S23 INCELL CON MARCO</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -10370,22 +10183,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>价格错误</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>iphone-incell-14</t>
+          <t>samsung-incell-s23-plus</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 14</t>
+          <t>Pantalla para Samsung S23 Plus</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>iPhone 14 INCELL FHD</t>
+          <t>Samsung S23 Plus INCELL CON MARCO</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -10393,22 +10206,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>价格错误</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>iphone-incell-14plus</t>
+          <t>samsung-incell-s24</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 14 Plus</t>
+          <t>Pantalla para Samsung S24</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>iPhone 14 Plus INCELL FHD</t>
+          <t>Samsung S24 INCELL CON MARCO</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -10416,3567 +10229,25 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>价格错误</t>
+          <t>视频缺失</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>iphone-incell-15plus</t>
+          <t>samsung-incell-s24-plus</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Pantalla para iPhone 15 Plus</t>
+          <t>Pantalla para Samsung S24 Plus</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>iPhone 15 Plus INCELL FHD</t>
+          <t>Samsung S24 Plus INCELL CON MARCO</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>价格错误</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>iphone-oled-13promax</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 13 Pro Max</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>iPhone 13 Pro Max OLED PREMIUM</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>价格错误</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>samsung-incell-s20-plus</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung S20 Plus</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Samsung S20 Plus INCELL CON MARCO</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>价格错误</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>samsung-incell-s9-plus</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung S9 Plus</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Samsung S9 Plus INCELL CON MARCO</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-x-pantalla-para-iphone-x</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone X</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-xs-pantalla-para-iphone-xs</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone XS</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>XS</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-xs-pantalla-para-iphone-xs</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone XS</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>XS</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-xr-pantalla-para-iphone-xr</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone XR</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>XR</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-11-pantalla-para-iphone-11</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 11</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-11-pantalla-para-iphone-11</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 11</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-11pro-pantalla-para-iphone-11pro</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 11PRO</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>11PRO</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-xs-max-pantalla-para-iphone-xs-max</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone XS MAX</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>XS MAX</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-xs-max-pantalla-para-iphone-xs-max</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone XS MAX</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>XS MAX</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-11pro-max-pantalla-para-iphone-11pro-max</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 11PRO MAX</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>11PRO MAX</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-11pro-max-pantalla-para-iphone-11pro-max</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 11PRO MAX</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>11PRO MAX</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-12mini-pantalla-para-iphone-12mini</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 12mini</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>12mini</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-12-12pro-pantalla-para-iphone-12-12pro</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 12/12PRO</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>12/12PRO</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-12-12pro-pantalla-para-iphone-12-12pro</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 12/12PRO</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>12/12PRO</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-12pro-max-pantalla-para-iphone-12pro-max</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 12PRO MAX</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>12PRO MAX</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-12pro-max-pantalla-para-iphone-12pro-max</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 12PRO MAX</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>12PRO MAX</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-13-mini-pantalla-para-iphone-13-mini</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 13 mini</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>13 mini</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-13-pantalla-para-iphone-13</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 13</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-13-pantalla-para-iphone-13</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 13</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-13pro-pantalla-para-iphone-13pro</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 13PRO</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>13PRO</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-13pro-pantalla-para-iphone-13pro</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 13PRO</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>13PRO</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-13pro-max-pantalla-para-iphone-13pro-max</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 13PRO MAX</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>13PRO MAX</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-13pro-max-pantalla-para-iphone-13pro-max</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 13PRO MAX</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>13PRO MAX</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-14-pantalla-para-iphone-14</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 14</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-14-pantalla-para-iphone-14</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 14</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-14-plus-pantalla-para-iphone-14-plus</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 14 plus</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>14 plus</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-14-plus-pantalla-para-iphone-14-plus</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 14 plus</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>14 plus</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-14pro-pantalla-para-iphone-14pro</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 14PRO</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>14PRO</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-14pro-pantalla-para-iphone-14pro</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 14PRO</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>14PRO</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-14pro-max-pantalla-para-iphone-14pro-max</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 14PRO MAX</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>14PRO MAX</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-14pro-max-pantalla-para-iphone-14pro-max</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 14PRO MAX</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>14PRO MAX</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-15-pantalla-para-iphone-15</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 15</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-15-pantalla-para-iphone-15</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 15</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-15-plus-pantalla-para-iphone-15-plus</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 15 plus</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>15 plus</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-15pro-pantalla-para-iphone-15pro</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 15PRO</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>15PRO</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-15pro-pantalla-para-iphone-15pro</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 15PRO</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>15PRO</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-15pro-max-pantalla-para-iphone-15pro-max</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 15PRO MAX</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>15PRO MAX</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-15pro-max-pantalla-para-iphone-15pro-max</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 15PRO MAX</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>15PRO MAX</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-16-pantalla-para-iphone-16</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 16</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-16e-pantalla-para-iphone-16e</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 16E</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>16E</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-16e-pantalla-para-iphone-16e</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 16E</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>16E</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-16plus-pantalla-para-iphone-16plus</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 16PLUS</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>16PLUS</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-16pro-pantalla-para-iphone-16pro</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 16PRO</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>16PRO</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-16pro-pantalla-para-iphone-16pro</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 16PRO</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>16PRO</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-16-promax-pantalla-para-iphone-16-promax</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 16 PROMAX</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>16 PROMAX</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-16-promax-pantalla-para-iphone-16-promax</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 16 PROMAX</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>16 PROMAX</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-17-pantalla-para-iphone-17</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 17</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-17pro-pantalla-para-iphone-17pro</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 17PRO</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>17PRO</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-17-air-pantalla-para-iphone-17-air</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 17 AIR</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>17 AIR</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-17e-pantalla-para-iphone-17e</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 17E</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>17E</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>图片缺失</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-17-promax-pantalla-para-iphone-17-promax</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 17 PROMAX</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>17 PROMAX</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>aimb-g5-ai-sports</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>AIMB-G5 AI SPORTS</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Gafas AI deportivas</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>iphone-incell-16e</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 16e</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>iPhone 16e INCELL FHD</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>iphone-incell-16plus</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 16 Plus</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>iPhone 16 Plus INCELL FHD</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>iphone-incell-16pro</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 16 Pro</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>iPhone 16 Pro INCELL FHD</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>iphone-incell-16promax</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 16 Pro Max</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>iPhone 16 Pro Max INCELL FHD</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>iphone-incell-17</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 17</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>iPhone 17 INCELL FHD</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>iphone-incell-17air</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 17 Air</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>iPhone 17 Air INCELL FHD</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>iphone-incell-17pro</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 17 Pro</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>iPhone 17 Pro INCELL FHD</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>iphone-incell-17promax</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 17 Pro Max</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>iPhone 17 Pro Max INCELL FHD</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>iphone-oled-16promax</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 16 Pro Max Soft OLED</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>iPhone 16 Pro Max SOFT OLED PREMIUM MOVE IC</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>micas-hd-clear-50</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Micas HD Clear</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>Paquete 50 piezas</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>micas-mate-corte</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Micas Mate</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>Peliculas para corte</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>micas-privacidad-corte</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Micas Privacidad</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>Peliculas privacy</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>s1-ai-classic</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>HAODE AI CLASSIC S1</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>Gafas AI classic</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>samsung-incell-note-10-plus</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung Note 10 Plus</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>Samsung Note 10 Plus INCELL CON MARCO</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>samsung-incell-note-20-ultra</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung Note 20 Ultra</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>Samsung Note 20 Ultra INCELL CON MARCO</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>samsung-incell-note-8</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung Note 8</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>Samsung Note 8 INCELL CON MARCO</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>samsung-incell-note-9</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung Note 9</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>Samsung Note 9 INCELL CON MARCO</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>samsung-incell-s20-ultra</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung S20 Ultra</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>Samsung S20 Ultra INCELL CON MARCO</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>samsung-incell-s21</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung S21</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>Samsung S21 INCELL CON MARCO</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>samsung-incell-s21-ultra</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung S21 Ultra</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>Samsung S21 Ultra INCELL CON MARCO</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>samsung-incell-s24-ultra</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung S24 Ultra</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>Samsung S24 Ultra INCELL CON MARCO</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>samsung-incell-s8</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung S8</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>Samsung S8 INCELL CON MARCO</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>samsung-incell-s9</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung S9</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>Samsung S9 INCELL CON MARCO</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>samsung-incell-s9-plus</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung S9 Plus</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>Samsung S9 Plus INCELL CON MARCO</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>samsung-oled-note-10</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung Note 10</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>Samsung Note 10 OLED CON MARCO</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>samsung-oled-note-10-plus</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung Note 10 Plus</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>Samsung Note 10 Plus OLED CON MARCO</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>samsung-oled-note-20</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung Note 20</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>Samsung Note 20 OLED CON MARCO</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>samsung-oled-note-20-ultra</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung Note 20 Ultra</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>Samsung Note 20 Ultra OLED CON MARCO</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>samsung-oled-note-9</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung Note 9</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>Samsung Note 9 OLED CON MARCO</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>samsung-oled-s20</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung S20</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>Samsung S20 OLED CON MARCO</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>samsung-oled-s20-ultra</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung S20 Ultra</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>Samsung S20 Ultra OLED CON MARCO</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>samsung-oled-s21</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung S21</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>Samsung S21 OLED CON MARCO</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>samsung-oled-s21-plus</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung S21 Plus</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>Samsung S21 Plus OLED CON MARCO</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>samsung-oled-s22-plus</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung S22 Plus</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>Samsung S22 Plus OLED CON MARCO</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>samsung-oled-s23-plus</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung S23 Plus</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>Samsung S23 Plus OLED CON MARCO</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>samsung-oled-s24-plus</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung S24 Plus</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>Samsung S24 Plus OLED CON MARCO</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr"/>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>samsung-oled-s9-plus</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung S9 Plus</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>Samsung S9 Plus OLED CON MARCO</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr"/>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>w630-ai-pro</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>W630 AI PRO</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>Gafas AI blancas</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>x200t-cortadora-micas</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>HAODE X200T Cortadora Inteligente de Micas</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>X200T</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-x-pantalla-para-iphone-x</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone X</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-xs-pantalla-para-iphone-xs</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone XS</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>XS</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-xs-pantalla-para-iphone-xs</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone XS</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>XS</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-xr-pantalla-para-iphone-xr</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone XR</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>XR</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-11-pantalla-para-iphone-11</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 11</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-11-pantalla-para-iphone-11</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 11</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-11pro-pantalla-para-iphone-11pro</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 11PRO</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>11PRO</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-xs-max-pantalla-para-iphone-xs-max</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone XS MAX</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>XS MAX</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-xs-max-pantalla-para-iphone-xs-max</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone XS MAX</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>XS MAX</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr"/>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-11pro-max-pantalla-para-iphone-11pro-max</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 11PRO MAX</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>11PRO MAX</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-11pro-max-pantalla-para-iphone-11pro-max</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 11PRO MAX</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>11PRO MAX</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr"/>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-12mini-pantalla-para-iphone-12mini</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 12mini</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>12mini</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr"/>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-12-12pro-pantalla-para-iphone-12-12pro</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 12/12PRO</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>12/12PRO</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr"/>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-12-12pro-pantalla-para-iphone-12-12pro</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 12/12PRO</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>12/12PRO</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr"/>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-12pro-max-pantalla-para-iphone-12pro-max</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 12PRO MAX</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>12PRO MAX</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr"/>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-12pro-max-pantalla-para-iphone-12pro-max</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 12PRO MAX</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>12PRO MAX</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr"/>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-13-mini-pantalla-para-iphone-13-mini</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 13 mini</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>13 mini</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr"/>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-13-pantalla-para-iphone-13</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 13</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr"/>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-13-pantalla-para-iphone-13</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 13</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr"/>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-13pro-pantalla-para-iphone-13pro</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 13PRO</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>13PRO</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr"/>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-13pro-pantalla-para-iphone-13pro</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 13PRO</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>13PRO</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr"/>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-13pro-max-pantalla-para-iphone-13pro-max</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 13PRO MAX</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>13PRO MAX</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr"/>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-13pro-max-pantalla-para-iphone-13pro-max</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 13PRO MAX</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>13PRO MAX</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr"/>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-14-pantalla-para-iphone-14</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 14</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr"/>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-14-pantalla-para-iphone-14</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 14</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr"/>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-14-plus-pantalla-para-iphone-14-plus</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 14 plus</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>14 plus</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr"/>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-14-plus-pantalla-para-iphone-14-plus</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 14 plus</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>14 plus</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr"/>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-14pro-pantalla-para-iphone-14pro</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 14PRO</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>14PRO</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr"/>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-14pro-pantalla-para-iphone-14pro</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 14PRO</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>14PRO</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr"/>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-14pro-max-pantalla-para-iphone-14pro-max</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 14PRO MAX</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>14PRO MAX</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr"/>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-14pro-max-pantalla-para-iphone-14pro-max</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 14PRO MAX</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>14PRO MAX</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr"/>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-15-pantalla-para-iphone-15</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 15</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr"/>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-15-pantalla-para-iphone-15</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 15</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr"/>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-15-plus-pantalla-para-iphone-15-plus</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 15 plus</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>15 plus</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr"/>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-15pro-pantalla-para-iphone-15pro</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 15PRO</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>15PRO</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr"/>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-15pro-pantalla-para-iphone-15pro</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 15PRO</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>15PRO</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr"/>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-15pro-max-pantalla-para-iphone-15pro-max</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 15PRO MAX</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>15PRO MAX</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr"/>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-15pro-max-pantalla-para-iphone-15pro-max</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 15PRO MAX</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>15PRO MAX</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr"/>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-16-pantalla-para-iphone-16</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 16</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr"/>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-16e-pantalla-para-iphone-16e</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 16E</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>16E</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr"/>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-16e-pantalla-para-iphone-16e</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 16E</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>16E</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr"/>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-16plus-pantalla-para-iphone-16plus</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 16PLUS</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>16PLUS</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr"/>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-16pro-pantalla-para-iphone-16pro</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 16PRO</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>16PRO</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr"/>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-16pro-pantalla-para-iphone-16pro</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 16PRO</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>16PRO</t>
-        </is>
-      </c>
-      <c r="E218" t="inlineStr"/>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-oled-iphone-16-promax-pantalla-para-iphone-16-promax</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 16 PROMAX</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>16 PROMAX</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr"/>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-16-promax-pantalla-para-iphone-16-promax</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 16 PROMAX</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>16 PROMAX</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr"/>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-17-pantalla-para-iphone-17</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 17</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="E221" t="inlineStr"/>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-17pro-pantalla-para-iphone-17pro</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 17PRO</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>17PRO</t>
-        </is>
-      </c>
-      <c r="E222" t="inlineStr"/>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-17-air-pantalla-para-iphone-17-air</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 17 AIR</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>17 AIR</t>
-        </is>
-      </c>
-      <c r="E223" t="inlineStr"/>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-17e-pantalla-para-iphone-17e</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 17E</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>17E</t>
-        </is>
-      </c>
-      <c r="E224" t="inlineStr"/>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>pantallas-iphone-incell-iphone-17-promax-pantalla-para-iphone-17-promax</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Pantalla para iPhone 17 PROMAX</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>17 PROMAX</t>
-        </is>
-      </c>
-      <c r="E225" t="inlineStr"/>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>samsung-incell-s10e</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung S10E</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>Samsung S10E INCELL CON MARCO</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr"/>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>samsung-incell-s21-fe</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung S21 FE</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>Samsung S21 FE INCELL CON MARCO</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr"/>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>samsung-incell-s21-plus</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung S21 Plus</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>Samsung S21 Plus INCELL CON MARCO</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr"/>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>samsung-incell-s22</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung S22</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>Samsung S22 INCELL CON MARCO</t>
-        </is>
-      </c>
-      <c r="E229" t="inlineStr"/>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>samsung-incell-s22-plus</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung S22 Plus</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>Samsung S22 Plus INCELL CON MARCO</t>
-        </is>
-      </c>
-      <c r="E230" t="inlineStr"/>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>samsung-incell-s23</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung S23</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>Samsung S23 INCELL CON MARCO</t>
-        </is>
-      </c>
-      <c r="E231" t="inlineStr"/>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>samsung-incell-s23-plus</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung S23 Plus</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>Samsung S23 Plus INCELL CON MARCO</t>
-        </is>
-      </c>
-      <c r="E232" t="inlineStr"/>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>samsung-incell-s24</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung S24</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>Samsung S24 INCELL CON MARCO</t>
-        </is>
-      </c>
-      <c r="E233" t="inlineStr"/>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>视频缺失</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>samsung-incell-s24-plus</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>Pantalla para Samsung S24 Plus</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>Samsung S24 Plus INCELL CON MARCO</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13984,6 +10255,1749 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="47" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>产品名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>型号</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>分类</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ignored_by_product_control</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>原因</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-incell-iphone-11-pantalla-para-iphone-11</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 11</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone INCELL</t>
+        </is>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-incell-iphone-11pro-max-pantalla-para-iphone-11pro-max</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 11PRO MAX</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>11PRO MAX</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone INCELL</t>
+        </is>
+      </c>
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-incell-iphone-11pro-pantalla-para-iphone-11pro</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 11PRO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>11PRO</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone INCELL</t>
+        </is>
+      </c>
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-incell-iphone-12-12pro-pantalla-para-iphone-12-12pro</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 12/12PRO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12/12PRO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone INCELL</t>
+        </is>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-incell-iphone-12mini-pantalla-para-iphone-12mini</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 12mini</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>12mini</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone INCELL</t>
+        </is>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-incell-iphone-12pro-max-pantalla-para-iphone-12pro-max</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 12PRO MAX</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>12PRO MAX</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone INCELL</t>
+        </is>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-incell-iphone-13-mini-pantalla-para-iphone-13-mini</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 13 mini</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>13 mini</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone INCELL</t>
+        </is>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-incell-iphone-13-pantalla-para-iphone-13</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 13</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone INCELL</t>
+        </is>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-incell-iphone-13pro-max-pantalla-para-iphone-13pro-max</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 13PRO MAX</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>13PRO MAX</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone INCELL</t>
+        </is>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-incell-iphone-13pro-pantalla-para-iphone-13pro</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 13PRO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>13PRO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone INCELL</t>
+        </is>
+      </c>
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-incell-iphone-14-pantalla-para-iphone-14</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 14</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone INCELL</t>
+        </is>
+      </c>
+      <c r="E12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-incell-iphone-14-plus-pantalla-para-iphone-14-plus</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 14 plus</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>14 plus</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone INCELL</t>
+        </is>
+      </c>
+      <c r="E13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-incell-iphone-14pro-max-pantalla-para-iphone-14pro-max</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 14PRO MAX</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>14PRO MAX</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone INCELL</t>
+        </is>
+      </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-incell-iphone-14pro-pantalla-para-iphone-14pro</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 14PRO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>14PRO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone INCELL</t>
+        </is>
+      </c>
+      <c r="E15" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-incell-iphone-15-pantalla-para-iphone-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 15</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone INCELL</t>
+        </is>
+      </c>
+      <c r="E16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-incell-iphone-15-plus-pantalla-para-iphone-15-plus</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 15 plus</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>15 plus</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone INCELL</t>
+        </is>
+      </c>
+      <c r="E17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-incell-iphone-15pro-max-pantalla-para-iphone-15pro-max</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 15PRO MAX</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>15PRO MAX</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone INCELL</t>
+        </is>
+      </c>
+      <c r="E18" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-incell-iphone-15pro-pantalla-para-iphone-15pro</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 15PRO</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>15PRO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone INCELL</t>
+        </is>
+      </c>
+      <c r="E19" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-incell-iphone-16-pantalla-para-iphone-16</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 16</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone INCELL</t>
+        </is>
+      </c>
+      <c r="E20" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" t="b">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-incell-iphone-16-promax-pantalla-para-iphone-16-promax</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 16 PROMAX</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>16 PROMAX</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone INCELL</t>
+        </is>
+      </c>
+      <c r="E21" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-incell-iphone-16e-pantalla-para-iphone-16e</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 16E</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>16E</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone INCELL</t>
+        </is>
+      </c>
+      <c r="E22" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-incell-iphone-16plus-pantalla-para-iphone-16plus</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 16PLUS</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>16PLUS</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone INCELL</t>
+        </is>
+      </c>
+      <c r="E23" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-incell-iphone-16pro-pantalla-para-iphone-16pro</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 16PRO</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>16PRO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone INCELL</t>
+        </is>
+      </c>
+      <c r="E24" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24" t="b">
+        <v>1</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-incell-iphone-17-air-pantalla-para-iphone-17-air</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 17 AIR</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>17 AIR</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone INCELL</t>
+        </is>
+      </c>
+      <c r="E25" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" t="b">
+        <v>1</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-incell-iphone-17-pantalla-para-iphone-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone INCELL</t>
+        </is>
+      </c>
+      <c r="E26" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26" t="b">
+        <v>1</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-incell-iphone-17-promax-pantalla-para-iphone-17-promax</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 17 PROMAX</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>17 PROMAX</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone INCELL</t>
+        </is>
+      </c>
+      <c r="E27" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" t="b">
+        <v>1</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-incell-iphone-17e-pantalla-para-iphone-17e</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 17E</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>17E</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone INCELL</t>
+        </is>
+      </c>
+      <c r="E28" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-incell-iphone-17pro-pantalla-para-iphone-17pro</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 17PRO</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>17PRO</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone INCELL</t>
+        </is>
+      </c>
+      <c r="E29" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-incell-iphone-x-pantalla-para-iphone-x</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone X</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone INCELL</t>
+        </is>
+      </c>
+      <c r="E30" t="b">
+        <v>1</v>
+      </c>
+      <c r="F30" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-incell-iphone-xr-pantalla-para-iphone-xr</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone XR</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>XR</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone INCELL</t>
+        </is>
+      </c>
+      <c r="E31" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-incell-iphone-xs-max-pantalla-para-iphone-xs-max</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone XS MAX</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>XS MAX</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone INCELL</t>
+        </is>
+      </c>
+      <c r="E32" t="b">
+        <v>1</v>
+      </c>
+      <c r="F32" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-incell-iphone-xs-pantalla-para-iphone-xs</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone XS</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone INCELL</t>
+        </is>
+      </c>
+      <c r="E33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-oled-iphone-11-pantalla-para-iphone-11</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 11</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone OLED</t>
+        </is>
+      </c>
+      <c r="E34" t="b">
+        <v>1</v>
+      </c>
+      <c r="F34" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-oled-iphone-11pro-max-pantalla-para-iphone-11pro-max</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 11PRO MAX</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>11PRO MAX</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone OLED</t>
+        </is>
+      </c>
+      <c r="E35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-oled-iphone-12-12pro-pantalla-para-iphone-12-12pro</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 12/12PRO</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>12/12PRO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone OLED</t>
+        </is>
+      </c>
+      <c r="E36" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-oled-iphone-12pro-max-pantalla-para-iphone-12pro-max</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 12PRO MAX</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>12PRO MAX</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone OLED</t>
+        </is>
+      </c>
+      <c r="E37" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-oled-iphone-13-pantalla-para-iphone-13</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 13</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone OLED</t>
+        </is>
+      </c>
+      <c r="E38" t="b">
+        <v>1</v>
+      </c>
+      <c r="F38" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-oled-iphone-13pro-max-pantalla-para-iphone-13pro-max</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 13PRO MAX</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>13PRO MAX</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone OLED</t>
+        </is>
+      </c>
+      <c r="E39" t="b">
+        <v>1</v>
+      </c>
+      <c r="F39" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-oled-iphone-13pro-pantalla-para-iphone-13pro</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 13PRO</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>13PRO</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone OLED</t>
+        </is>
+      </c>
+      <c r="E40" t="b">
+        <v>1</v>
+      </c>
+      <c r="F40" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-oled-iphone-14-pantalla-para-iphone-14</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 14</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone OLED</t>
+        </is>
+      </c>
+      <c r="E41" t="b">
+        <v>1</v>
+      </c>
+      <c r="F41" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-oled-iphone-14-plus-pantalla-para-iphone-14-plus</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 14 plus</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>14 plus</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone OLED</t>
+        </is>
+      </c>
+      <c r="E42" t="b">
+        <v>1</v>
+      </c>
+      <c r="F42" t="b">
+        <v>1</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-oled-iphone-14pro-max-pantalla-para-iphone-14pro-max</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 14PRO MAX</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>14PRO MAX</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone OLED</t>
+        </is>
+      </c>
+      <c r="E43" t="b">
+        <v>1</v>
+      </c>
+      <c r="F43" t="b">
+        <v>1</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-oled-iphone-14pro-pantalla-para-iphone-14pro</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 14PRO</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>14PRO</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone OLED</t>
+        </is>
+      </c>
+      <c r="E44" t="b">
+        <v>1</v>
+      </c>
+      <c r="F44" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-oled-iphone-15-pantalla-para-iphone-15</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 15</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone OLED</t>
+        </is>
+      </c>
+      <c r="E45" t="b">
+        <v>1</v>
+      </c>
+      <c r="F45" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-oled-iphone-15pro-max-pantalla-para-iphone-15pro-max</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 15PRO MAX</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>15PRO MAX</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone OLED</t>
+        </is>
+      </c>
+      <c r="E46" t="b">
+        <v>1</v>
+      </c>
+      <c r="F46" t="b">
+        <v>1</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-oled-iphone-15pro-pantalla-para-iphone-15pro</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 15PRO</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>15PRO</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone OLED</t>
+        </is>
+      </c>
+      <c r="E47" t="b">
+        <v>1</v>
+      </c>
+      <c r="F47" t="b">
+        <v>1</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-oled-iphone-16-promax-pantalla-para-iphone-16-promax</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 16 PROMAX</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>16 PROMAX</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone OLED</t>
+        </is>
+      </c>
+      <c r="E48" t="b">
+        <v>1</v>
+      </c>
+      <c r="F48" t="b">
+        <v>1</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-oled-iphone-16e-pantalla-para-iphone-16e</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 16E</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>16E</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone OLED</t>
+        </is>
+      </c>
+      <c r="E49" t="b">
+        <v>1</v>
+      </c>
+      <c r="F49" t="b">
+        <v>1</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-oled-iphone-16pro-pantalla-para-iphone-16pro</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone 16PRO</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>16PRO</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone OLED</t>
+        </is>
+      </c>
+      <c r="E50" t="b">
+        <v>1</v>
+      </c>
+      <c r="F50" t="b">
+        <v>1</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-oled-iphone-xs-max-pantalla-para-iphone-xs-max</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone XS MAX</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>XS MAX</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone OLED</t>
+        </is>
+      </c>
+      <c r="E51" t="b">
+        <v>1</v>
+      </c>
+      <c r="F51" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>pantallas-iphone-oled-iphone-xs-pantalla-para-iphone-xs</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Pantalla para iPhone XS</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Pantallas iPhone OLED</t>
+        </is>
+      </c>
+      <c r="E52" t="b">
+        <v>1</v>
+      </c>
+      <c r="F52" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>价格表派生 SKU；Firestore / 网站 / App 三端均未上线；不纳入健康统计</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14045,7 +12059,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6">

--- a/data/products-master.xlsx
+++ b/data/products-master.xlsx
@@ -581,7 +581,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -641,7 +641,6 @@
           <t>/haode-web/assets/products/productos-ai/aimb-g5-ai-smart-glasses/main.jpg</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>缺平台 / 视频缺失</t>
@@ -681,7 +680,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -689,7 +688,6 @@
           <t>/haode-web/assets/products/productos-ai/w630-ai-smart-glasses/main.jpg</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>缺平台 / 视频缺失</t>
@@ -729,7 +727,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -737,7 +735,6 @@
           <t>/haode-web/assets/products/productos-ai/s1-ai-classic/main.png</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>缺平台 / 视频缺失</t>
@@ -785,7 +782,6 @@
           <t>/haode-web/assets/products/micas-hd-clear/main.png</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>缺平台 / 视频缺失</t>
@@ -833,7 +829,6 @@
           <t>/haode-web/assets/products/home-cut-machine/micas-mate.svg</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>缺平台 / 视频缺失</t>
@@ -881,7 +876,6 @@
           <t>/haode-web/assets/products/home-cut-machine/micas-privacidad.svg</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>缺平台 / 视频缺失</t>
@@ -929,7 +923,6 @@
           <t>/haode-web/assets/products/cut-machine/x200t/main.jpg</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>缺平台 / 视频缺失</t>
@@ -964,12 +957,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>550</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>530</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1016,12 +1009,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>550</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>530</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1029,7 +1022,6 @@
           <t>/haode-web/assets/products/samsung-incell/note-10-plus/main.jpg</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>视频缺失</t>
@@ -1064,12 +1056,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>680</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>670</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1077,7 +1069,6 @@
           <t>/haode-web/assets/products/samsung-incell/note-20-ultra/main.jpg</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>视频缺失</t>
@@ -1112,12 +1103,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>480</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1125,7 +1116,6 @@
           <t>/haode-web/assets/products/samsung-incell/note-8/main.jpg</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>视频缺失</t>
@@ -1160,12 +1150,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>500</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>480</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1173,7 +1163,6 @@
           <t>/haode-web/assets/products/samsung-incell/note-9/main.jpg</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>视频缺失</t>
@@ -1208,12 +1197,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>380</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>370</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1260,12 +1249,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>380</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>370</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1312,12 +1301,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>580</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1325,7 +1314,6 @@
           <t>/haode-web/assets/products/samsung-incell/s10e/main.jpg</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>视频缺失</t>
@@ -1469,7 +1457,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>530</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1529,7 +1517,6 @@
           <t>/haode-web/assets/products/samsung-incell/s20-ultra/main.jpg</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>视频缺失</t>
@@ -1577,7 +1564,6 @@
           <t>/haode-web/assets/products/samsung-incell/s21-fe/main.jpg</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>视频缺失</t>
@@ -1625,7 +1611,6 @@
           <t>/haode-web/assets/products/samsung-incell/s21/main.jpg</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>视频缺失</t>
@@ -1673,7 +1658,6 @@
           <t>/haode-web/assets/products/samsung-incell/s21-plus/main.jpg</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>视频缺失</t>
@@ -1708,12 +1692,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>550</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>530</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1721,7 +1705,6 @@
           <t>/haode-web/assets/products/samsung-incell/s21-ultra/main.jpg</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>视频缺失</t>
@@ -1756,12 +1739,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>500</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>480</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1769,7 +1752,6 @@
           <t>/haode-web/assets/products/samsung-incell/s22/main.jpg</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>视频缺失</t>
@@ -1804,12 +1786,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>500</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>480</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1817,7 +1799,6 @@
           <t>/haode-web/assets/products/samsung-incell/s22-plus/main.jpg</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>视频缺失</t>
@@ -1852,12 +1833,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>580</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1904,12 +1885,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>580</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1917,7 +1898,6 @@
           <t>/haode-web/assets/products/samsung-incell/s23/main.jpg</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>视频缺失</t>
@@ -1952,12 +1932,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>580</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1965,7 +1945,6 @@
           <t>/haode-web/assets/products/samsung-incell/s23-plus/main.jpg</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>视频缺失</t>
@@ -2000,12 +1979,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>650</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>630</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2052,12 +2031,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>700</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>680</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2065,7 +2044,6 @@
           <t>/haode-web/assets/products/samsung-incell/s24/main.png</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>视频缺失</t>
@@ -2100,12 +2078,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>700</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>680</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2113,7 +2091,6 @@
           <t>/haode-web/assets/products/samsung-incell/s24-plus/main.jpg</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>视频缺失</t>
@@ -2148,12 +2125,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>750</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>740</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2161,7 +2138,6 @@
           <t>/haode-web/assets/products/samsung-incell/s24-ultra/main.jpg</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>视频缺失</t>
@@ -2196,12 +2172,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>360</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>350</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2209,7 +2185,6 @@
           <t>/haode-web/assets/products/samsung-incell/s8/main.jpg</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>视频缺失</t>
@@ -2244,12 +2219,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>370</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>360</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2296,12 +2271,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>360</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>350</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2309,7 +2284,6 @@
           <t>/haode-web/assets/products/samsung-incell/s9/main.jpg</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>视频缺失</t>
@@ -2344,12 +2318,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>370</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>360</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2357,7 +2331,6 @@
           <t>/haode-web/assets/products/samsung-incell/s9-plus/main.jpg</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>价格异常 / 视频缺失</t>
@@ -2405,7 +2378,6 @@
           <t>/haode-web/assets/products/samsung-oled/note-10/main.jpg</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>视频缺失</t>
@@ -2453,7 +2425,6 @@
           <t>/haode-web/assets/products/samsung-oled/note-10-plus/main.jpg</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>视频缺失</t>
@@ -2501,7 +2472,6 @@
           <t>/haode-web/assets/products/samsung-oled/note-20/main.jpg</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>视频缺失</t>
@@ -2549,7 +2519,6 @@
           <t>/haode-web/assets/products/samsung-oled/note-20-ultra/main.jpg</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>视频缺失</t>
@@ -2582,14 +2551,11 @@
           <t>Pantalla para Samsung Note 9</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>/haode-web/assets/products/samsung-oled/note-9/main.jpg</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>缺平台 / 视频缺失</t>
@@ -2622,14 +2588,11 @@
           <t>Pantalla para Samsung S20</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>/haode-web/assets/products/samsung-oled/s20/main.jpg</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>缺平台 / 视频缺失</t>
@@ -2714,14 +2677,11 @@
           <t>Pantalla para Samsung S20 Ultra</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>/haode-web/assets/products/samsung-oled/s20-ultra/main.jpg</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>缺平台 / 视频缺失</t>
@@ -2754,14 +2714,11 @@
           <t>Pantalla para Samsung S21</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>/haode-web/assets/products/samsung-oled/s21/main.jpg</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>缺平台 / 视频缺失</t>
@@ -2794,14 +2751,11 @@
           <t>Pantalla para Samsung S21 Plus</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>/haode-web/assets/products/samsung-oled/s21-plus/main.jpg</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>缺平台 / 视频缺失</t>
@@ -2886,14 +2840,11 @@
           <t>Pantalla para Samsung S22 Plus</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>/haode-web/assets/products/samsung-oled/s22-plus/main.jpg</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>缺平台 / 视频缺失</t>
@@ -2978,14 +2929,11 @@
           <t>Pantalla para Samsung S23 Plus</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>/haode-web/assets/products/samsung-oled/s23-plus/main.jpg</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>缺平台 / 视频缺失</t>
@@ -3070,14 +3018,11 @@
           <t>Pantalla para Samsung S24 Plus</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>/haode-web/assets/products/samsung-oled/s24-plus/main.jpg</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>缺平台 / 视频缺失</t>
@@ -3214,14 +3159,11 @@
           <t>Pantalla para Samsung S9 Plus</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>/haode-web/assets/products/samsung-oled/s9-plus/main.jpg</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>缺平台 / 视频缺失</t>
@@ -3264,8 +3206,6 @@
           <t>175</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -3308,8 +3248,6 @@
           <t>195</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -3352,8 +3290,6 @@
           <t>210</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -3396,8 +3332,6 @@
           <t>210</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -3440,8 +3374,6 @@
           <t>240</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -3484,8 +3416,6 @@
           <t>220</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -3528,8 +3458,6 @@
           <t>245</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -3572,8 +3500,6 @@
           <t>250</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -3616,8 +3542,6 @@
           <t>290</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -3660,8 +3584,6 @@
           <t>340</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -3704,8 +3626,6 @@
           <t>250</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -3748,8 +3668,6 @@
           <t>290</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -3792,8 +3710,6 @@
           <t>340</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -3836,8 +3752,6 @@
           <t>350</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -3880,8 +3794,6 @@
           <t>290</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -3924,8 +3836,6 @@
           <t>310</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -3968,8 +3878,6 @@
           <t>340</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -4012,8 +3920,6 @@
           <t>380</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -4056,8 +3962,6 @@
           <t>380</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -4100,8 +4004,6 @@
           <t>730</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -4144,8 +4046,6 @@
           <t>280</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -4188,8 +4088,6 @@
           <t>380</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -4232,8 +4130,6 @@
           <t>680</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -4276,8 +4172,6 @@
           <t>950</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -4320,8 +4214,6 @@
           <t>2400</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -4364,8 +4256,6 @@
           <t>850</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -4408,8 +4298,6 @@
           <t>950</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -4452,8 +4340,6 @@
           <t>800</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -4496,8 +4382,6 @@
           <t>175</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -4540,8 +4424,6 @@
           <t>175</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -4584,8 +4466,6 @@
           <t>175</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -4628,8 +4508,6 @@
           <t>190</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -4721,7 +4599,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>190</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -5665,7 +5543,6 @@
           <t>/haode-web/assets/products/iphone-incell/16plus/main.jpg</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
           <t>视频缺失</t>
@@ -5713,7 +5590,6 @@
           <t>/haode-web/assets/products/iphone-incell/16pro/main.jpg</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
           <t>视频缺失</t>
@@ -5761,7 +5637,6 @@
           <t>/haode-web/assets/products/iphone-incell/16promax/main.jpg</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
           <t>视频缺失</t>
@@ -5796,12 +5671,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>380</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5809,7 +5684,6 @@
           <t>/haode-web/assets/products/iphone-incell/16e/main.jpg</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
           <t>视频缺失</t>
@@ -5857,7 +5731,6 @@
           <t>/haode-web/assets/products/iphone-incell/17air/main.jpg</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
           <t>视频缺失</t>
@@ -5905,7 +5778,6 @@
           <t>/haode-web/assets/products/iphone-incell/17/main.jpg</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>视频缺失</t>
@@ -5953,7 +5825,6 @@
           <t>/haode-web/assets/products/iphone-incell/17pro/main.jpg</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>视频缺失</t>
@@ -6001,7 +5872,6 @@
           <t>/haode-web/assets/products/iphone-incell/17promax/main.jpg</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>视频缺失</t>
@@ -6242,14 +6112,11 @@
           <t>Pantalla para iPhone 11</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
           <t>185</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -6292,8 +6159,6 @@
           <t>590</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -6336,8 +6201,6 @@
           <t>640</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -6380,8 +6243,6 @@
           <t>830</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -6424,8 +6285,6 @@
           <t>720</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -6468,8 +6327,6 @@
           <t>780</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -6512,8 +6369,6 @@
           <t>850</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -6556,8 +6411,6 @@
           <t>950</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -6600,8 +6453,6 @@
           <t>1150</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -6644,8 +6495,6 @@
           <t>1150</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -6688,8 +6537,6 @@
           <t>950</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -6732,8 +6579,6 @@
           <t>1150</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -6776,8 +6621,6 @@
           <t>1250</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -6820,8 +6663,6 @@
           <t>1100</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -6864,8 +6705,6 @@
           <t>1950</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -6908,8 +6747,6 @@
           <t>720</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -6952,8 +6789,6 @@
           <t>1450</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -6996,8 +6831,6 @@
           <t>180</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -7040,8 +6873,6 @@
           <t>570</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
           <t>ignored_by_product_control=true / historical=true</t>
@@ -7180,12 +7011,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>700</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>680</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -7282,8 +7113,6 @@
           <t>Pantalla para iPhone 12 mini</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
           <t>/haode-web/assets/products/iphone-oled/12mini/main.jpg</t>
@@ -7333,7 +7162,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>700</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -7380,12 +7209,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>800</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>780</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -7432,12 +7261,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>780</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>760</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -7482,8 +7311,6 @@
           <t>Pantalla para iPhone 13 mini</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
           <t>/haode-web/assets/products/iphone-oled/13mini/main.jpg</t>
@@ -7786,8 +7613,6 @@
           <t>Pantalla para iPhone 15 Plus</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
           <t>/haode-web/assets/products/iphone-oled/15plus/main.jpg</t>
@@ -7882,8 +7707,6 @@
           <t>Pantalla para iPhone 16</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
         <is>
           <t>/haode-web/assets/products/iphone-oled/16/main.jpg</t>
@@ -7926,8 +7749,6 @@
           <t>Pantalla para iPhone 16 Plus</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr">
         <is>
           <t>/haode-web/assets/products/iphone-oled/16plus/main.jpg</t>
@@ -7972,12 +7793,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -8037,7 +7858,6 @@
           <t>/haode-web/assets/products/iphone-oled/16promax/main.jpg</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
           <t>视频缺失</t>
@@ -8072,12 +7892,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -8982,7 +8802,6 @@
           <t>iPhone 12 Pro Max INCELL FHD</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -9005,7 +8824,6 @@
           <t>iPhone 14 INCELL FHD</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9028,7 +8846,6 @@
           <t>iPhone 14 Plus INCELL FHD</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9051,7 +8868,6 @@
           <t>iPhone 15 Plus INCELL FHD</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9074,7 +8890,6 @@
           <t>iPhone 13 Pro Max OLED PREMIUM</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9097,7 +8912,6 @@
           <t>Samsung S20 Plus INCELL CON MARCO</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9120,7 +8934,6 @@
           <t>Samsung S9 Plus INCELL CON MARCO</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -9143,7 +8956,6 @@
           <t>Gafas AI deportivas</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -9166,7 +8978,6 @@
           <t>iPhone 16e INCELL FHD</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -9189,7 +9000,6 @@
           <t>iPhone 16 Plus INCELL FHD</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -9212,7 +9022,6 @@
           <t>iPhone 16 Pro INCELL FHD</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -9235,7 +9044,6 @@
           <t>iPhone 16 Pro Max INCELL FHD</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -9258,7 +9066,6 @@
           <t>iPhone 17 INCELL FHD</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -9281,7 +9088,6 @@
           <t>iPhone 17 Air INCELL FHD</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -9304,7 +9110,6 @@
           <t>iPhone 17 Pro INCELL FHD</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -9327,7 +9132,6 @@
           <t>iPhone 17 Pro Max INCELL FHD</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -9350,7 +9154,6 @@
           <t>iPhone 16 Pro Max SOFT OLED PREMIUM MOVE IC</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -9373,7 +9176,6 @@
           <t>Paquete 50 piezas</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -9396,7 +9198,6 @@
           <t>Peliculas para corte</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -9419,7 +9220,6 @@
           <t>Peliculas privacy</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -9442,7 +9242,6 @@
           <t>Gafas AI classic</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -9465,7 +9264,6 @@
           <t>Samsung Note 10 Plus INCELL CON MARCO</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -9488,7 +9286,6 @@
           <t>Samsung Note 20 Ultra INCELL CON MARCO</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -9511,7 +9308,6 @@
           <t>Samsung Note 8 INCELL CON MARCO</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -9534,7 +9330,6 @@
           <t>Samsung Note 9 INCELL CON MARCO</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -9557,7 +9352,6 @@
           <t>Samsung S20 Ultra INCELL CON MARCO</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -9580,7 +9374,6 @@
           <t>Samsung S21 INCELL CON MARCO</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -9603,7 +9396,6 @@
           <t>Samsung S21 Ultra INCELL CON MARCO</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -9626,7 +9418,6 @@
           <t>Samsung S24 Ultra INCELL CON MARCO</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -9649,7 +9440,6 @@
           <t>Samsung S8 INCELL CON MARCO</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -9672,7 +9462,6 @@
           <t>Samsung S9 INCELL CON MARCO</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -9695,7 +9484,6 @@
           <t>Samsung S9 Plus INCELL CON MARCO</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -9718,7 +9506,6 @@
           <t>Samsung Note 10 OLED CON MARCO</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -9741,7 +9528,6 @@
           <t>Samsung Note 10 Plus OLED CON MARCO</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -9764,7 +9550,6 @@
           <t>Samsung Note 20 OLED CON MARCO</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -9787,7 +9572,6 @@
           <t>Samsung Note 20 Ultra OLED CON MARCO</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -9810,7 +9594,6 @@
           <t>Samsung Note 9 OLED CON MARCO</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -9833,7 +9616,6 @@
           <t>Samsung S20 OLED CON MARCO</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -9856,7 +9638,6 @@
           <t>Samsung S20 Ultra OLED CON MARCO</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -9879,7 +9660,6 @@
           <t>Samsung S21 OLED CON MARCO</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -9902,7 +9682,6 @@
           <t>Samsung S21 Plus OLED CON MARCO</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -9925,7 +9704,6 @@
           <t>Samsung S22 Plus OLED CON MARCO</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -9948,7 +9726,6 @@
           <t>Samsung S23 Plus OLED CON MARCO</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -9971,7 +9748,6 @@
           <t>Samsung S24 Plus OLED CON MARCO</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -9994,7 +9770,6 @@
           <t>Samsung S9 Plus OLED CON MARCO</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -10017,7 +9792,6 @@
           <t>Gafas AI blancas</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -10040,7 +9814,6 @@
           <t>X200T</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -10063,7 +9836,6 @@
           <t>Samsung S10E INCELL CON MARCO</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -10086,7 +9858,6 @@
           <t>Samsung S21 FE INCELL CON MARCO</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -10109,7 +9880,6 @@
           <t>Samsung S21 Plus INCELL CON MARCO</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -10132,7 +9902,6 @@
           <t>Samsung S22 INCELL CON MARCO</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -10155,7 +9924,6 @@
           <t>Samsung S22 Plus INCELL CON MARCO</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -10178,7 +9946,6 @@
           <t>Samsung S23 INCELL CON MARCO</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -10201,7 +9968,6 @@
           <t>Samsung S23 Plus INCELL CON MARCO</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -10224,7 +9990,6 @@
           <t>Samsung S24 INCELL CON MARCO</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -10247,7 +10012,6 @@
           <t>Samsung S24 Plus INCELL CON MARCO</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
